--- a/data/uac_network.xlsx
+++ b/data/uac_network.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10512"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/SystemDocumentation/github/uactechdoc/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE4D1455-7781-DD45-BCBF-3D10F4CEC56F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AA39746-9A99-5146-8E51-C134F9C85D77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{C276EF8E-8567-464E-98DC-2A8DA10DDBB6}"/>
   </bookViews>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="270">
   <si>
     <t>NSCU-A004</t>
   </si>
@@ -876,6 +876,18 @@
   </si>
   <si>
     <t>amp room</t>
+  </si>
+  <si>
+    <t>192.168.201.104</t>
+  </si>
+  <si>
+    <t>192.168.201.106</t>
+  </si>
+  <si>
+    <t>2601-2800</t>
+  </si>
+  <si>
+    <t>2507-0700</t>
   </si>
 </sst>
 </file>
@@ -991,7 +1003,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1008,6 +1020,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1379,7 +1392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BC7A309-0B6A-4549-9590-6CFCF97D2DB0}">
-  <dimension ref="A1:L53"/>
+  <dimension ref="A1:L55"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.6640625" customWidth="1"/>
@@ -3115,6 +3128,28 @@
       </c>
       <c r="K53" t="s">
         <v>265</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A54" s="14" t="s">
+        <v>269</v>
+      </c>
+      <c r="B54" t="s">
+        <v>108</v>
+      </c>
+      <c r="I54" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A55" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="B55" t="s">
+        <v>108</v>
+      </c>
+      <c r="I55" t="s">
+        <v>267</v>
       </c>
     </row>
   </sheetData>
